--- a/src/utils/sxsyzlzq/friends/guyue/zz_guyue_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/guyue/zz_guyue_level.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10725" windowHeight="11385" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="11340" windowHeight="10515" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="禅意" sheetId="6" r:id="rId1"/>
     <sheet name="帝国" sheetId="7" r:id="rId2"/>
     <sheet name="冬神" sheetId="10" r:id="rId3"/>
-    <sheet name="蛮石" sheetId="8" r:id="rId4"/>
+    <sheet name="隐秘" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="68">
   <si>
     <t>名称</t>
   </si>
@@ -50,48 +50,27 @@
     <t>长耳庄巧姑</t>
   </si>
   <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>雪狐剑客</t>
-  </si>
-  <si>
     <t>连击</t>
   </si>
   <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
     <t>小计：</t>
   </si>
   <si>
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>传记·月落</t>
+    <t>蟠桃隐士</t>
   </si>
   <si>
     <t>宫廷乐师</t>
   </si>
   <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
     <t>雪山飞狐</t>
   </si>
   <si>
-    <t>当铺掌柜</t>
-  </si>
-  <si>
-    <t>御风武者</t>
-  </si>
-  <si>
     <t>百刺浪客</t>
   </si>
   <si>
@@ -125,6 +104,12 @@
     <t>雪域春光·凛</t>
   </si>
   <si>
+    <t>逍遥居士·铭</t>
+  </si>
+  <si>
+    <t>豪情禅师·悟能</t>
+  </si>
+  <si>
     <t>橙色卡等：</t>
   </si>
   <si>
@@ -134,18 +119,12 @@
     <t>禅意卡等：</t>
   </si>
   <si>
-    <t>炫目神光</t>
-  </si>
-  <si>
     <t>圣殿弩手</t>
   </si>
   <si>
     <t>田园守望者</t>
   </si>
   <si>
-    <t>增援战线</t>
-  </si>
-  <si>
     <t>光明惩戒</t>
   </si>
   <si>
@@ -155,6 +134,9 @@
     <t>四芒军旗</t>
   </si>
   <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
     <t>白袍主教</t>
   </si>
   <si>
@@ -164,15 +146,15 @@
     <t>召集护卫</t>
   </si>
   <si>
-    <t>夺取阵地</t>
-  </si>
-  <si>
     <t>圣枪·卡洛琳</t>
   </si>
   <si>
     <t>明日之音·露娜</t>
   </si>
   <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
@@ -185,12 +167,12 @@
     <t>骨爆</t>
   </si>
   <si>
-    <t>战场遗迹</t>
-  </si>
-  <si>
     <t>转化仪式</t>
   </si>
   <si>
+    <t>阴冷墓穴</t>
+  </si>
+  <si>
     <t>寒风草人</t>
   </si>
   <si>
@@ -200,67 +182,58 @@
     <t>神庙魔像</t>
   </si>
   <si>
-    <t>极地狂信者</t>
-  </si>
-  <si>
     <t>绝望之地</t>
   </si>
   <si>
-    <t>寒冰骨墙</t>
+    <t>寒彻骨</t>
   </si>
   <si>
     <t>冰峰甲虫</t>
   </si>
   <si>
-    <t>咒杀酷吏</t>
-  </si>
-  <si>
     <t>寒风血刃</t>
   </si>
   <si>
-    <t>冰野荒芜计划</t>
-  </si>
-  <si>
     <t>永夜女王</t>
   </si>
   <si>
     <t>冬神卡等：</t>
   </si>
   <si>
-    <t>愚笨鲸头鹅</t>
-  </si>
-  <si>
-    <t>势如破竹</t>
-  </si>
-  <si>
-    <t>蓄力射手</t>
-  </si>
-  <si>
-    <t>生命源力</t>
-  </si>
-  <si>
-    <t>强行捕猎</t>
-  </si>
-  <si>
-    <t>无畏猎户</t>
-  </si>
-  <si>
-    <t>诱敌草人</t>
-  </si>
-  <si>
-    <t>肥鼠晚宴</t>
-  </si>
-  <si>
-    <t>活力仙人</t>
-  </si>
-  <si>
-    <t>飞斧狂人</t>
-  </si>
-  <si>
-    <t>飞斧女豪</t>
-  </si>
-  <si>
-    <t>蛮石卡等：</t>
+    <t>洞悉之眼</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>沉重否定</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1197,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1251,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1262,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1284,7 +1257,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1299,103 +1272,103 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>21.2</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C14" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2">
         <v>3</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C15" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1">
-        <f>AVERAGE(C2:C12)</f>
-        <v>19.5454545454545</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="C17" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1403,10 +1376,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1414,198 +1387,143 @@
         <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="2">
-        <v>3</v>
-      </c>
-      <c r="C21" s="2">
-        <v>14</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="2">
-        <v>4</v>
-      </c>
-      <c r="C22" s="2">
-        <v>20</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C12:C20)</f>
+        <v>18.4444444444444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B27" s="3">
+        <v>3</v>
+      </c>
+      <c r="C27" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="3">
         <v>4</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C28" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="2">
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="3">
         <v>4</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C29" s="3">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="2">
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="3">
         <v>4</v>
       </c>
-      <c r="C25" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="2">
+      <c r="C30" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="3">
         <v>5</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C31" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="2">
-        <v>5</v>
-      </c>
-      <c r="C27" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="2">
-        <f>AVERAGE(C18:C27)</f>
-        <v>17.2</v>
+      <c r="B32" s="3">
+        <v>6</v>
+      </c>
+      <c r="C32" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="3">
-        <v>3</v>
-      </c>
-      <c r="C33" s="3">
-        <v>19</v>
-      </c>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="3">
-        <v>3</v>
-      </c>
-      <c r="C34" s="3">
-        <v>12</v>
-      </c>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="3">
+        <f>AVERAGE(C26:C32)</f>
+        <v>17.8571428571429</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="3">
-        <v>4</v>
-      </c>
-      <c r="C35" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="3">
-        <v>4</v>
-      </c>
-      <c r="C36" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" s="3">
-        <v>4</v>
-      </c>
-      <c r="C37" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="3">
-        <f>AVERAGE(C33:C37)</f>
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C43" s="4">
-        <f>AVERAGE(C2:C12,C18:C27,C33:C37)</f>
-        <v>18.1153846153846</v>
+      <c r="C38" s="4">
+        <f>AVERAGE(C2:C6,C12:C20,C26:C32)</f>
+        <v>18.9047619047619</v>
       </c>
     </row>
   </sheetData>
@@ -1615,289 +1533,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="1">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>19</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C13:C18)</f>
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="3">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="3">
-        <v>6</v>
-      </c>
-      <c r="C26" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="3">
-        <v>8</v>
-      </c>
-      <c r="C27" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C24:C27)</f>
-        <v>15.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C7,C13:C18,C24:C27)</f>
-        <v>17.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D32"/>
@@ -1921,7 +1556,279 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="1">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>19.75</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2">
+        <f>AVERAGE(C11:C16)</f>
+        <v>18.8333333333333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3">
+        <v>4</v>
+      </c>
+      <c r="C22" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3">
+        <v>4</v>
+      </c>
+      <c r="C23" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C22:C26)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C5,C11:C16,C22:C26)</f>
+        <v>18.4666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1932,235 +1839,202 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
-        <v>12</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="1">
-        <f>AVERAGE(C2:C10)</f>
-        <v>15.3333333333333</v>
-      </c>
-      <c r="D13" s="2"/>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>17.375</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2">
+        <f>AVERAGE(C15:C16)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="3">
         <v>3</v>
       </c>
-      <c r="C16" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="C22" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="3">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C16:C18)</f>
-        <v>14</v>
-      </c>
-    </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="3">
-        <v>3</v>
-      </c>
-      <c r="C24" s="3">
-        <v>14</v>
-      </c>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>12</v>
-      </c>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="3">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="C26" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+        <f>AVERAGE(C22:C23)</f>
+        <v>16.5</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C24:C26)</f>
-        <v>14.6666666666667</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C10,C16:C18,C24:C26)</f>
-        <v>14.9333333333333</v>
+      <c r="A29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="4">
+        <f>AVERAGE(C2:C9,C15:C16,C22:C23)</f>
+        <v>16.8333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2193,29 +2067,29 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -2226,158 +2100,154 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B7" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>14.5714285714286</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" customFormat="1"/>
+    <row r="13" customFormat="1"/>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="1">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1">
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="1">
-        <f>AVERAGE(C2:C10)</f>
-        <v>14.8888888888889</v>
-      </c>
-      <c r="D13" s="2"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
       </c>
       <c r="C17" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="2">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2">
-        <v>18</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2"/>
@@ -2385,20 +2255,28 @@
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="2">
-        <f>AVERAGE(C16:C21)</f>
-        <v>17.5</v>
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C14:C20)</f>
+        <v>15.1428571428571</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1"/>
+    <row r="25" customFormat="1"/>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2413,26 +2291,28 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="3" t="e">
-        <f>AVERAGE(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
+        <v>26</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C26:C26)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1"/>
+    <row r="31" customFormat="1"/>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C10,C16:C21)</f>
-        <v>15.9333333333333</v>
+        <f>AVERAGE(C2:C8,C14:C20,C26:C26)</f>
+        <v>14.6666666666667</v>
       </c>
     </row>
   </sheetData>
